--- a/tame_output/ON/bt/strategyON_20230818.xlsx
+++ b/tame_output/ON/bt/strategyON_20230818.xlsx
@@ -595,7 +595,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>46.3%</t>
+          <t>43.8%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -605,16 +605,16 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.68</t>
+          <t>0.64</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>53.2%</t>
+          <t>53.1%</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1689</v>
+        <v>1690</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -623,12 +623,12 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>2023-08-16</t>
+          <t>2023-08-17</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>67.5%</t>
+          <t>67.7%</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -652,7 +652,7 @@
         </is>
       </c>
       <c r="N2" t="n">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="O2" t="inlineStr">
         <is>
@@ -676,7 +676,7 @@
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>-11.5%</t>
+          <t>-11.8%</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -736,7 +736,7 @@
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>62.4%</t>
+          <t>54.8%</t>
         </is>
       </c>
     </row>
@@ -748,26 +748,26 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>81.7%</t>
+          <t>78.3%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>29.3%</t>
+          <t>29.6%</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2.78</t>
+          <t>2.65</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>59.6%</t>
+          <t>59.5%</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1689</v>
+        <v>1690</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -776,12 +776,12 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>2023-08-16</t>
+          <t>2023-08-17</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>30.8%</t>
+          <t>31.3%</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -809,7 +809,7 @@
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>-6.5%</t>
+          <t>-11.8%</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -829,7 +829,7 @@
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>-2.5%</t>
+          <t>-3.3%</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
@@ -839,17 +839,17 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>68.9%</t>
+          <t>65.9%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>23.5%</t>
+          <t>23.7%</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>2.9</t>
+          <t>2.8</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -859,7 +859,7 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>-5.3%</t>
+          <t>-5.0%</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
@@ -889,7 +889,7 @@
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>11.1%</t>
+          <t>3.1%</t>
         </is>
       </c>
     </row>
@@ -911,7 +911,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>0.97</t>
+          <t>0.96</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -920,7 +920,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1689</v>
+        <v>1690</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -929,7 +929,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>2023-08-16</t>
+          <t>2023-08-17</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -992,7 +992,7 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>53.9%</t>
+          <t>53.2%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
@@ -1002,7 +1002,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>2.2</t>
+          <t>2.1</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -1012,7 +1012,7 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>456.1%</t>
+          <t>454.8%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
@@ -1054,17 +1054,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>105.9%</t>
+          <t>102.1%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>32.0%</t>
+          <t>32.2%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>3.31</t>
+          <t>3.17</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1073,7 +1073,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1689</v>
+        <v>1690</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -1082,12 +1082,12 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>2023-08-16</t>
+          <t>2023-08-17</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>32.7%</t>
+          <t>33.1%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1115,12 +1115,12 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>-8.6%</t>
+          <t>-11.1%</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>-3.0%</t>
+          <t>-3.1%</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
@@ -1135,7 +1135,7 @@
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-2.8%</t>
+          <t>-3.6%</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
@@ -1145,17 +1145,17 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>101.8%</t>
+          <t>97.9%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>26.7%</t>
+          <t>26.9%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>3.8</t>
+          <t>3.6</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -1165,7 +1165,7 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-18.9%</t>
+          <t>-18.6%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
@@ -1195,7 +1195,7 @@
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>16.1%</t>
+          <t>8.1%</t>
         </is>
       </c>
     </row>
@@ -1212,7 +1212,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>25.0%</t>
+          <t>24.9%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1226,7 +1226,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1689</v>
+        <v>1690</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -1235,7 +1235,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>2023-08-16</t>
+          <t>2023-08-17</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1298,7 +1298,7 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>70.4%</t>
+          <t>69.9%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
@@ -1308,7 +1308,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>3.7</t>
+          <t>3.6</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -1360,17 +1360,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>138.3%</t>
+          <t>133.9%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>32.7%</t>
+          <t>32.9%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>4.23</t>
+          <t>4.07</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1379,7 +1379,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1689</v>
+        <v>1690</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -1388,12 +1388,12 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>2023-08-16</t>
+          <t>2023-08-17</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>33.1%</t>
+          <t>33.6%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1421,12 +1421,12 @@
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>-4.3%</t>
+          <t>-9.9%</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>-1.7%</t>
+          <t>-2.0%</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
@@ -1441,7 +1441,7 @@
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>-1.5%</t>
+          <t>-2.4%</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
@@ -1451,17 +1451,17 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>132.9%</t>
+          <t>128.4%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>27.2%</t>
+          <t>27.4%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>4.9</t>
+          <t>4.7</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -1471,7 +1471,7 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-14.8%</t>
+          <t>-14.5%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>16.2%</t>
+          <t>8.1%</t>
         </is>
       </c>
     </row>
@@ -1516,7 +1516,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G1692"/>
+  <dimension ref="A1:G1693"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -40426,7 +40426,7 @@
         <v>45154</v>
       </c>
       <c r="B1692" t="n">
-        <v>2.859500869275066</v>
+        <v>2.86013381293179</v>
       </c>
       <c r="C1692" t="n">
         <v>2.966107540648022</v>
@@ -40442,6 +40442,29 @@
       </c>
       <c r="G1692" t="n">
         <v>4.272466830616158</v>
+      </c>
+    </row>
+    <row r="1693">
+      <c r="A1693" s="2" t="n">
+        <v>45155</v>
+      </c>
+      <c r="B1693" t="n">
+        <v>2.783110157528106</v>
+      </c>
+      <c r="C1693" t="n">
+        <v>2.885591268694849</v>
+      </c>
+      <c r="D1693" t="n">
+        <v>1.549236405597689</v>
+      </c>
+      <c r="E1693" t="n">
+        <v>3.504929406620178</v>
+      </c>
+      <c r="F1693" t="n">
+        <v>2.177384335174791</v>
+      </c>
+      <c r="G1693" t="n">
+        <v>4.192021869799725</v>
       </c>
     </row>
   </sheetData>
